--- a/tests/workbooktests/workbooks/test_optimizers.xlsx
+++ b/tests/workbooktests/workbooks/test_optimizers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEB04A8-1A27-4C47-970E-26DE8CB0033D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F13DB856-4E74-45C0-8CA1-C37D63A2176F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" activeTab="1" xr2:uid="{E76B3670-D287-482D-903A-DB7A1E5EF242}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E76B3670-D287-482D-903A-DB7A1E5EF242}"/>
   </bookViews>
   <sheets>
     <sheet name="Constraints" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
   <si>
     <t>qlNoConstraint</t>
   </si>
@@ -170,14 +170,43 @@
   </si>
   <si>
     <t>qlLevenbergMarquardt</t>
+  </si>
+  <si>
+    <t>lower_bound</t>
+  </si>
+  <si>
+    <t>upper_bound</t>
+  </si>
+  <si>
+    <t>memory</t>
+  </si>
+  <si>
+    <t>pg_tol</t>
+  </si>
+  <si>
+    <t>f_tol</t>
+  </si>
+  <si>
+    <t>qlLBFGSB</t>
+  </si>
+  <si>
+    <t>qlLBFGSBBounded</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -193,7 +222,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -201,16 +230,100 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -226,7 +339,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -543,31 +656,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{327A04EB-76EE-4F21-BB1B-33964149D1F3}">
   <dimension ref="A2:B12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="e" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_xll.qlNoConstraint()</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="str" cm="1">
+        <f t="array" ref="B2">_xll.qlNoConstraint()</f>
+        <v>欣[test_optimizers.xlsx]Constraints!R2C2NoConstraint,A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="e" cm="1">
-        <f t="array" aca="1" ref="B3" ca="1">_xll.qlPositiveConstraint()</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" t="str" cm="1">
+        <f t="array" ref="B3">_xll.qlPositiveConstraint()</f>
+        <v>欣[test_optimizers.xlsx]Constraints!R3C2PositiveConstraint,A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -575,7 +688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -583,7 +696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -591,7 +704,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -599,31 +712,31 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="e" cm="1">
-        <f t="array" aca="1" ref="B10" ca="1">_xll.qlBoundaryConstraint(A6,B6)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" t="str" cm="1">
+        <f t="array" ref="B10">_xll.qlBoundaryConstraint(A6,B6)</f>
+        <v>欣[test_optimizers.xlsx]Constraints!R10C2BoundaryConstraint,A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" t="e" cm="1">
-        <f t="array" aca="1" ref="B11" ca="1">_xll.qlCompositeConstraint(B3,B10)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" t="str" cm="1">
+        <f t="array" ref="B11">_xll.qlCompositeConstraint(B3,B10)</f>
+        <v>欣[test_optimizers.xlsx]Constraints!R11C2CompositeConstraint,A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
-      <c r="B12" t="e" cm="1">
-        <f t="array" aca="1" ref="B12" ca="1">_xll.qlNonhomogeneousBoundaryConstraint(A6:A8,B6:B8)</f>
-        <v>#VALUE!</v>
+      <c r="B12" t="str" cm="1">
+        <f t="array" ref="B12">_xll.qlNonhomogeneousBoundaryConstraint(A6:A8,B6:B8)</f>
+        <v>欣[test_optimizers.xlsx]Constraints!R12C2NonhomogeneousBoundaryConstraint,A</v>
       </c>
     </row>
   </sheetData>
@@ -633,210 +746,300 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394B9001-4C2C-46EE-A1BD-66EDDB727756}">
-  <dimension ref="A2:E25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:C33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.33203125" customWidth="1"/>
+    <col min="1" max="1" width="35.28515625" customWidth="1"/>
+    <col min="2" max="2" width="58.28515625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>100</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="5">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="6">
         <v>1E-4</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="6">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="6">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="e" cm="1">
-        <f t="array" aca="1" ref="B8" ca="1">_xll.qlEndCriteria(B2,B3,B4,B5,B6)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B7" s="9" t="str" cm="1">
+        <f t="array" ref="B7">_xll.qlEndCriteria(B2,B3,B4,B5,B6)</f>
+        <v>欣[test_optimizers.xlsx]EndCriteria!R7C2EndCriteria,A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B8" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" t="e" cm="1">
-        <f t="array" aca="1" ref="B11" ca="1">_xll.qlEndCriteriaSucceded($B$8,A11)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B9" s="5" t="b" cm="1">
+        <f t="array" ref="B9">_xll.qlEndCriteriaSucceded($B$7,A9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="e" cm="1">
-        <f t="array" aca="1" ref="B12" ca="1">_xll.qlEndCriteriaSucceded($B$8,A12)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B10" s="5" t="b" cm="1">
+        <f t="array" ref="B10">_xll.qlEndCriteriaSucceded($B$7,A10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B13" t="e" cm="1">
-        <f t="array" aca="1" ref="B13" ca="1">_xll.qlEndCriteriaSucceded($B$8,A13)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B11" s="5" t="b" cm="1">
+        <f t="array" ref="B11">_xll.qlEndCriteriaSucceded($B$7,A11)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B14" t="e" cm="1">
-        <f t="array" aca="1" ref="B14" ca="1">_xll.qlEndCriteriaSucceded($B$8,A14)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B12" s="5" t="b" cm="1">
+        <f t="array" ref="B12">_xll.qlEndCriteriaSucceded($B$7,A12)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B15" t="e" cm="1">
-        <f t="array" aca="1" ref="B15" ca="1">_xll.qlEndCriteriaSucceded($B$8,A15)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B13" s="5" t="b" cm="1">
+        <f t="array" ref="B13">_xll.qlEndCriteriaSucceded($B$7,A13)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B16" t="e" cm="1">
-        <f t="array" aca="1" ref="B16" ca="1">_xll.qlEndCriteriaSucceded($B$8,A16)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B14" s="5" t="b" cm="1">
+        <f t="array" ref="B14">_xll.qlEndCriteriaSucceded($B$7,A14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B17" t="e" cm="1">
-        <f t="array" aca="1" ref="B17" ca="1">_xll.qlEndCriteriaSucceded($B$8,A17)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B15" s="9" t="b" cm="1">
+        <f t="array" ref="B15">_xll.qlEndCriteriaSucceded($B$7,A15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B17" s="10">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="E19" t="s">
+      <c r="C17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B18" s="6">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="E20" t="s">
+      <c r="C18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B19" s="6">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="E21" t="s">
+      <c r="C19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B22" t="b">
+      <c r="B20" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E22" t="s">
+      <c r="C20" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B24" t="e" cm="1">
-        <f t="array" aca="1" ref="B24" ca="1">_xll.qlLevenbergMarquardt()</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B21" s="5" t="str" cm="1">
+        <f t="array" ref="B21">_xll.qlLevenbergMarquardt()</f>
+        <v>欣[test_optimizers.xlsx]EndCriteria!R21C2LevenbergMarquardt,A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B25" t="e" cm="1">
-        <f t="array" aca="1" ref="B25" ca="1">_xll.qlLevenbergMarquardt(B19,B20,B21,B22)</f>
-        <v>#VALUE!</v>
+      <c r="B22" s="9" t="str" cm="1">
+        <f t="array" ref="B22">_xll.qlLevenbergMarquardt(B17,B18,B19,B20)</f>
+        <v>欣[test_optimizers.xlsx]EndCriteria!R22C2LevenbergMarquardt,A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6">
+        <v>1E-8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6">
+        <v>2.2204460492503102E-9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="str" cm="1">
+        <f t="array" ref="B30">_xll.qlLBFGSB()</f>
+        <v>欣[test_optimizers.xlsx]EndCriteria!R30C2LBFGSB,A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="str" cm="1">
+        <f t="array" ref="B31">_xll.qlLBFGSB(B27,B28,B29)</f>
+        <v>欣[test_optimizers.xlsx]EndCriteria!R31C2LBFGSB,A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="5" t="str" cm="1">
+        <f t="array" ref="B32">_xll.qlLBFGSBBounded(B23:B24,B25:B26)</f>
+        <v>欣[test_optimizers.xlsx]EndCriteria!R32C2LBFGSB,A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="9" t="str" cm="1">
+        <f t="array" ref="B33">_xll.qlLBFGSBBounded(B23:B24,B25:B26,B27,B28,B29)</f>
+        <v>欣[test_optimizers.xlsx]EndCriteria!R33C2LBFGSB,A</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>